--- a/campanhas/planejamento-t1-2026-2027/conteudos-t1.xlsx
+++ b/campanhas/planejamento-t1-2026-2027/conteudos-t1.xlsx
@@ -9,6 +9,18 @@
   <sheets>
     <sheet name="Guia de imagens" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Semana 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Semana 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Semana 3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Semana 4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Semana 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Semana 6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Semana 7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Semana 8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Semana 9" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Semana 10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Semana 11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Semana 12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Semana 13" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,12 +588,1451 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Prova social, depoimentos, semana de fechamento do trimestre</t>
+          <t>Prova social, depoimentos, semanas de fechamento de trimestre</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Pedir print de conversa (com autorização) ou foto que o próprio cliente mandou brindando com o vinho</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 2/nov</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Vale ou não vale?</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Tampa de rosca é pior?</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Vale ou não vale: vinho de tampa de rosca é pior que vinho de rolha?
+Não vale esse julgamento. A tampa de rosca é, tecnicamente, mais eficiente pra vedar e evitar contaminação. Vários produtores premiados na Austrália e Nova Zelândia usam só tampa de rosca, inclusive em vinhos de guarda.
+O que define qualidade é o que tem dentro da garrafa, não o que fecha ela.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 4/nov</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>O custo real de importar vinho</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Por que vinho importado custa o que custa: imposto de importação, câmbio, frete internacional, seguro, armazenagem refrigerada, mais a margem de quem importou e de quem vende.
+Cada etapa dessa soma no preço final. Entender isso ajuda a enxergar por que um vinho de R$150 lá fora chega aqui custando mais.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 6/nov</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Um vinho que você nunca ouviu falar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Rótulo pouco conhecido</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[nome de uva/vinho pouco conhecido], vindo de [região]. [completar com 1-2 frases de curiosidade]
+Um daqueles rótulos que merece mais atenção do que recebe.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa) + arte de apoio destacando a uva/região no rótulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 2/nov</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana: [2-3 vinhos].</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 4/nov</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor], [completar com detalhe de história/filosofia].</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 6/nov</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Dica rápida</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Mito da temperatura</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Mito comum: todo vinho tinto se serve em temperatura ambiente. Na prática, "ambiente" na Europa antigamente era mais frio que a sala aqui no Brasil.
+Ideal pra tinto encorpado: 16-18°C. Um pouco mais frio que o senso comum.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 5/nov</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Mitos do vinho</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Os mitos do vinho que a gente ouve toda semana
+Oi, [nome]
+Vinho caro é sempre melhor. Tampa de rosca é pior que rolha. Tinto se serve em temperatura ambiente. Três frases que a gente ouve sempre, e nenhuma delas é totalmente verdade.
+Separamos essa semana pra desmontar esses mitos, um por um, nas redes. Vale conferir antes da próxima garrafa.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 9/nov</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Uvas pouco conhecidas</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Tem muito mais uva no mundo do que Cabernet Sauvignon e Chardonnay. [completar com 2-3 uvas raras] são exemplos de castas que fazem vinhos incríveis mas nunca viram nome de prateleira de supermercado.
+Sair do óbvio é onde mora a parte mais interessante de beber vinho.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 11/nov</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Trazer uma uva rara pro Brasil</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Trazer uma uva rara pro Brasil geralmente significa lote pequeno, produtor pequeno e mais burocracia por garrafa, proporcionalmente, do que um lote grande de uva conhecida.
+Vale a pena mesmo assim, porque é isso que garante variedade real no catálogo.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 13/nov</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Um vinho que você nunca ouviu falar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Semana temática de descoberta</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[nome do vinho/uva rara]. [completar com detalhe de origem e característica]
+Se você é do time Explorador, esse é pra você.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa) + arte de apoio destacando a uva/região no rótulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 9/nov</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Raridades</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana com raridades de verdade: [2-3 vinhos de uvas raras]. Pra quem gosta de sair do óbvio.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 11/nov</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor pequeno</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor pequeno], produção artesanal em [região], [completar com detalhe].</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 13/nov</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Experimentar algo novo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana é uma boa desculpa pra sair da zona de conforto. Bora testar [nome do vinho raro]?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 12/nov</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3 vinhos que você nunca ouviu falar</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: 3 vinhos que você provavelmente nunca ouviu falar
+Oi, [nome]
+Separamos três rótulos de uvas raras que estão no catálogo e que quase ninguém pede por não conhecer. [completar com os 3 nomes e uma linha de descrição cada]
+Se você é do perfil Explorador, essa lista é especialmente pra você.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 16/nov</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>O que é vinho novo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Vinho novo é aquele engarrafado e vendido rápido, poucas semanas depois da colheita, sem passar tempo de guarda. O exemplo mais famoso é o Beaujolais Nouveau, da França, tradicionalmente liberado pra venda na terceira quinta-feira de novembro.
+É um vinho leve, frutado, feito pra beber jovem, não pra guardar. Curiosidade que rende boa conversa numa mesa.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 18/nov</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Vinho jovem x vinho de guarda</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Nem todo vinho é feito pra guardar. Uns são pensados pra beber logo, frescos e frutados. Outros são feitos pra evoluir na garrafa por anos.
+A diferença tá na estrutura: tanino, acidez e concentração determinam se aquele vinho vai melhorar com o tempo ou se o momento certo é agora.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 20/nov</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>O que estamos provando</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Vinho jovem da casa</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>O que estamos provando essa semana: [nome de um vinho jovem/leve do catálogo]. Fresco, frutado, sem pretensão de guarda.
+Às vezes o vinho mais gostoso é o mais simples.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 16/nov</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Vinhos jovens e frescos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana com vinhos jovens e frescos: [2-3 vinhos]. Pra beber já, sem cerimônia.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 19/nov</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Data comemorativa</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Beaujolais Nouveau</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Hoje é dia de Beaujolais Nouveau, a tradição francesa do vinho novo que sai da vinha direto pra taça em poucas semanas.
+[se tiver o rótulo no catálogo, oferecer aqui; senão, usar como gancho educativo pro perfil Explorador]</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 20/nov</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Sugestão de fim de semana</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Vinho jovem</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana com vinho jovem: [nome do vinho]. Simples, gostoso, sem enrolação.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 19/nov</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>A tradição do vinho novo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: A tradição do vinho novo (e por que ela existe)
+Oi, [nome]
+Hoje é o dia oficial do Beaujolais Nouveau, tradição francesa que libera pra venda um vinho colhido semanas antes, ainda jovem e frutado.
+É um jeito diferente de pensar vinho: nem todo rótulo precisa envelhecer pra ser bom. Alguns são feitos exatamente pra esse frescor do momento.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 23/nov</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Anúncio</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Campanha de Black Friday</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Black Friday chegando e a comnéctar separou uma seleção especial pra essa semana. Vinhos que a gente ama, com condição que só acontece uma vez no ano.
+Fica de olho, a lista completa sai nos próximos dias.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte de campanha com identidade visual + destaque "Black Friday comnéctar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 25/nov</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Como monta a seleção de Black Friday</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Montar a seleção de Black Friday não é só pegar o que sobrou de estoque. A gente escolhe rótulos que realmente valem o desconto, pensando no perfil de cada cliente que já respondeu o quiz.
+Desconto bom em vinho ruim não é oferta, é só puxar preço pra baixo.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 27/nov</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Oferta do dia</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Black Friday no ar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>É hoje. Black Friday da comnéctar no ar com [detalhe da oferta].
+Link na bio pra ver a seleção completa antes que acabe.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Arte de oferta com preço/desconto em destaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 23/nov</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Aquecimento</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Essa semana tem oferta</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Essa semana tem oferta grande por aqui. Black Friday da comnéctar chega sexta-feira, com seleção especial de vinhos escolhidos a dedo.
+Se prepara 👀</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 25/nov</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Prévia</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Lista da seleção de Black Friday</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>A seleção de Black Friday já pode ser conferida: [lista de vinhos com desconto].
+Sexta-feira é o dia oficial, mas quem quiser garantir antes pode chamar aqui.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 27/nov</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Disparo do dia</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Oferta de Black Friday</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Black Friday no ar! [detalhe da oferta] só até domingo.
+[link] — não deixa pra depois, os melhores rótulos costumam esgotar primeiro.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 26/nov</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Campanha de Black Friday</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Black Friday comnéctar: a seleção está no ar
+Oi, [nome]
+Preparamos uma seleção de Black Friday pensada pra valer a pena de verdade, não só desconto por desconto. [detalhe da oferta] em rótulos que a gente escolheu com carinho.
+Vale garantir o seu antes que a seleção acabe.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 30/nov</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Diário da comnéctar</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Retrospectiva do trimestre</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Fechando os primeiros 90 dias do novo posicionamento da comnéctar. Lançamos o quiz, o Mapa do Vinho, e [número de leads, se disponível] pessoas já descobriram o próprio perfil de vinho.
+Foi só o começo. Tem muita coisa boa vindo por aí.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 2/dez</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Prova social</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Depoimentos do trimestre</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[espaço reservado pra depoimentos reais de clientes que já usaram o quiz ou compraram baseado no perfil — coletar antes de publicar]
+Ver esse tipo de retorno é o motivo de a gente ter mudado o foco pra descoberta.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Print ou foto enviada pelo cliente (pedir autorização antes de publicar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 4/dez</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Teaser</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>O que vem no próximo trimestre</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>O que vem por aí: programa de indicação, kits temáticos pensados por perfil e sim, o Natal já tá no radar.
+Fica ligado, tem trimestre novo chegando com novidade boa.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 30/nov</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana: [2-3 vinhos]. Fechando o trimestre com boas garrafas.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 2/dez</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Último convite</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Quem ainda não fez o quiz</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Se você ainda não respondeu o quiz de perfil de vinho, essa é a hora. Foram quase 90 dias de gente descobrindo qual é o seu jeito de beber vinho, e ainda dá tempo de entrar nessa.
+[link do quiz]</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 4/dez</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Agradecimento</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Spoiler do T2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fechando o trimestre com um obrigado. Muita coisa boa vem no próximo: indicação, kits novos e surpresas de fim de ano.
+Bom fim de semana e obrigado por fazer parte disso 🍷</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 3/dez</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Fechamento do trimestre + spoiler indicação</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Fechando o trimestre (e o que vem a seguir)
+Oi, [nome]
+Nesses últimos 90 dias a comnéctar mudou de foco: de só vender vinho pra te ajudar a descobrir vinho. Lançamos o quiz de perfil, o guia Mapa do Vinho, e [métrica se disponível] de vocês já participaram.
+O próximo trimestre vem com programa de indicação (spoiler: você vai poder ganhar algo por trazer um amigo), kits temáticos pensados pro seu perfil, e a temporada de fim de ano se aproximando.
+Obrigado por caminhar com a gente nesse começo.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
         </is>
       </c>
     </row>
@@ -669,7 +2120,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Foto de bastidores/lifestyle — você entre garrafas, adega ou mesa de seleção. Formato feed 1080x1350</t>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
         </is>
       </c>
     </row>
@@ -703,7 +2154,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Foto de bastidores — caixas de importação, planilha de seleção, degustação. Formato feed 1080x1350</t>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
         </is>
       </c>
     </row>
@@ -805,7 +2256,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor) + foto de produto</t>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
         </is>
       </c>
     </row>
@@ -884,4 +2335,2040 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 14/set</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Diário da comnéctar</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Dia do Cliente (15/set)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Amanhã é Dia do Cliente, e aqui na comnéctar isso não é só uma data de marketing.
+Cada garrafa que sai daqui carrega uma conversa que já tivemos antes: o que você gosta, o que já provou, o que ainda quer descobrir. É esse vaivém que faz a curadoria funcionar de verdade.
+Obrigado por fazer parte disso.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 16/set</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Curadoria pensada pro cliente</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Toda vez que um vinho novo entra no catálogo, a pergunta não é só "esse vinho é bom?". É "pra quem esse vinho é bom?".
+Tem cliente que quer segurança, tem cliente que quer ser surpreendido, tem cliente que só quer um tinto gostoso pro jantar de sexta. A curadoria tenta responder isso antes de qualquer rótulo chegar na loja.
+É por isso que dois clientes diferentes recebem sugestões diferentes por aqui, mesmo comprando na mesma loja.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 18/set</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Prova social</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Depoimento de cliente</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[Espaço reservado pra depoimento real — print de conversa ou trecho de avaliação, com autorização antes de publicar]
+Legenda de apoio: "É pra ouvir isso que a gente trabalha. Obrigado, [nome do cliente], por confiar na seleção."</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Print ou foto enviada pelo cliente (pedir autorização antes de publicar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 14/set</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Oferta</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Oferta especial Dia do Cliente</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amanhã é Dia do Cliente e queremos comemorar com você. [detalhe da oferta — desconto ou frete grátis] em qualquer pedido até domingo.
+Passa lá na loja e escolhe o seu 🍷</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 16/set</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor], em [região], faz vinho do jeito que aprendeu com [avô/família/geração anterior].
+[completar com 1-2 frases sobre o processo ou filosofia]
+Esse é um dos rótulos que carrega mais história no catálogo.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 18/set</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Agradecimento</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Sugestão de fim de semana</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fechando a semana do Dia do Cliente com um obrigado de verdade. A sugestão pra hoje é o [nome do vinho], ótimo pra abrir com quem você gosta de ter por perto.
+Bom fim de semana 🍷</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 17/set</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Dia do Cliente com oferta</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Um obrigado (com desconto)
+Oi, [nome]
+Hoje é Dia do Cliente e a gente queria fazer diferente de só mandar um "feliz dia".
+Cada pedido seu ajudou a gente a entender melhor o que funciona: quais vinhos vale a pena trazer, quais produtores merecem mais espaço no catálogo, o que realmente faz sentido pra quem compra aqui.
+Como agradecimento, deixamos [detalhe da oferta] até domingo.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 21/set</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Vinhos pra receber a primavera</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>A primavera chega dia 23 e com ela a vontade muda: menos vinho encorpado pra esquentar, mais vinho leve pra acompanhar tarde de sol.
+Rosés, brancos frescos e espumantes ganham espaço nessa época. Temperatura mais alta costuma pedir taninos mais suaves e acidez mais viva.
+Se ainda não testou um rosé seco, essa é a estação certa pra começar.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 23/set</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>O que estamos provando</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Os 4 tipos de bebedor de vinho</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Toda pessoa que bebe vinho se encaixa, mais ou menos, em um desses perfis:
+Quem gosta de descobrir coisas novas. Quem prefere ir no seguro. Quem busca uma experiência mais sofisticada. Quem só quer praticidade no dia a dia.
+Nenhum é melhor que o outro, só pedem curadorias diferentes. Em breve a gente te ajuda a descobrir o seu.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 25/set</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Story enquete</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Teaser do quiz</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Story com sticker de enquete: "Fim de semana pede tinto encorpado ou vinho leve?"
+Legenda de apoio: "Guarda a resposta, ela vai fazer sentido em breve 👀"</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto simples de fundo (taça ou garrafa) com o sticker de enquete por cima</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 21/set</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Leves de primavera</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Semana de primavera chegando e a seleção de hoje é pros leves: [2-3 vinhos leves/rosés/espumantes do catálogo].
+Combina com tarde de sol, terraço, mesa ao ar livre. Responde aqui se quiser separar algum.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 23/set</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Teaser</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Semana que vem tem novidade</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Prepara que semana que vem tem novidade por aqui. Uma ferramenta nova pra te ajudar a descobrir exatamente o tipo de vinho que combina com você.
+Fica de olho no Instagram e no WhatsApp 👀</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 25/set</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Harmonização</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana de primavera</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana de primavera pede algo leve na mesa. [nome do vinho] combina bem com [sugestão de prato leve — salada, peixe, queijo fresco].
+Bom fim de semana!</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 24/set</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Teaser do quiz</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Você sabe qual é o seu perfil de vinho?
+Oi, [nome]
+Tem gente que bebe vinho pra descobrir coisa nova toda semana. Tem gente que prefere repetir o que já sabe que gosta. Tem gente que busca uma experiência mais rara, e tem gente que só quer facilidade no dia a dia.
+Nenhum desses perfis é errado, mas cada um pede uma curadoria diferente.
+Na próxima semana a gente lança uma ferramenta nova pra te ajudar a descobrir exatamente o seu perfil, e a partir daí toda sugestão que você receber da comnéctar vai ser pensada pra ele.
+Fica de olho no seu email na semana que vem.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 28/set</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Quiz oficialmente no ar</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Chegou. O quiz que te ajuda a descobrir qual é o seu perfil de vinho está no ar.
+Duas perguntas, dois minutos, e você recebe recomendações pensadas pro seu jeito de beber vinho, não pro genérico.
+Link na bio pra responder.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte de lançamento com identidade visual + botão/CTA do quiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 30/set</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Guia</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Destaque do Mapa do Vinho</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Junto com o resultado do quiz vem um presente: o Mapa do Vinho, um guia gratuito com o que a gente mais recebe de pergunta por aqui.
+Como escolher vinho sem se perder no rótulo. Harmonizações básicas. Temperatura certa pra servir. Erros mais comuns na hora de guardar uma garrafa.
+Responde o quiz (link na bio) e ele chega direto no seu email.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mockup/capa do guia Mapa do Vinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 2/out</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Diário da comnéctar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Bastidor da construção do quiz</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Semanas construindo isso com o Tiago: cada pergunta do quiz foi pensada pra realmente dizer alguma coisa sobre como você bebe vinho, não só preencher formulário.
+Testamos, ajustamos, testamos de novo. Curioso pra ver o que sai disso.
+Já respondeu? Link na bio.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 28/set</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Disparo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Anúncio do quiz pra base</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Novidade no ar! Lançamos o quiz da comnéctar pra descobrir qual é o seu perfil de vinho.
+Responde em 2 minutos e já recebe um guia gratuito de presente: [link do quiz]</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 30/set</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Reforço</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Prova social do quiz</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Já tem gente respondendo o quiz e descobrindo perfil que nem imaginava (spoiler: bastante gente se identificou como Explorador).
+Ainda não fez o seu? [link do quiz]</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 2/out</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Convite direto</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Último lembrete da semana</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Só passando pra lembrar: o quiz de perfil de vinho tá no ar e leva menos tempo que escolher o que assistir hoje à noite.
+[link do quiz] — e o resultado já vem com um guia de presente.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 1/out</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Quiz + guia pra toda a lista</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: O quiz que te ajuda a escolher vinho melhor está no ar
+Oi, [nome]
+Chegou a ferramenta que a gente comentou semana passada: o quiz de perfil de vinho da comnéctar.
+Em dois minutos você descobre se é mais Explorador, Clássico, Sofisticado ou Casual, e a partir daí a gente ajusta as recomendações pro seu jeito de beber vinho.
+De brinde, o resultado vem acompanhado do Mapa do Vinho, nosso guia gratuito com o que a gente mais explica pra quem tá começando a se interessar por vinho de verdade.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 5/out</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Rosés e brancos leves</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rosé não é "vinho de menina" nem branco é só pra quem "não gosta de vinho de verdade". Esses rótulos leves pedem tanta técnica quanto qualquer tinto encorpado.
+A diferença tá no perfil: acidez mais viva, menos tanino, servido bem gelado. Ótimo pra clima quente e pra quem tá começando a explorar vinho sem se assustar.
+Bora testar um esse fim de semana?</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 7/out</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Como brancos e rosés chegam até aqui</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Vinho branco e rosé têm um desafio a mais na importação: a temperatura durante o transporte importa ainda mais que nos tintos, porque a acidez e o frescor se perdem fácil.
+Isso muda como a gente escolhe transportadora e armazenamento pra esses rótulos especificamente.
+Detalhe que ninguém vê, mas que faz diferença no copo.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 9/out</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Um vinho que você nunca ouviu falar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Uva branca rara</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[nome da uva branca pouco conhecida], uma uva que praticamente ninguém no Brasil conhece, mas que faz vinhos brancos surpreendentes em [região].
+[completar com 1-2 frases de curiosidade sobre a uva]
+Já ouviu falar? A gente tem esse rótulo no catálogo.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa) + arte de apoio destacando a uva/região no rótulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 5/out</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Leves e refrescantes</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana pros dias mais quentes: [2-3 vinhos leves/rosés/brancos]. Combina com fim de tarde no terraço.
+Quer que a gente separe algum?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 7/out</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor de espumante</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor de espumante], que faz espumante em [região] há [X anos/gerações], é conhecido por [detalhe do método/filosofia].
+Um dos espumantes mais queridos do catálogo vem de lá.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 9/out</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Harmonização</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana de primavera</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Pro fim de semana: [nome do vinho] combina bem com [prato leve, ex: salmão, salada, queijo fresco]. Serve bem gelado.
+Bom fim de semana!</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 8/out</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Guia rápido de vinhos leves</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: O guia rápido de vinhos leves pra primavera
+Oi, [nome]
+Com o clima esquentando, vale trocar um pouco o repertório: rosés secos, brancos frescos e espumantes ganham espaço na mesa.
+Separamos [2-3 sugestões do catálogo] pra você começar por aí. Todos servidos bem gelados, entre 6°C e 10°C.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 12/out</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Como ler um rótulo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rótulo de vinho parece código secreto até você aprender os pontos principais: safra (o ano da colheita), região ou appellation, e às vezes a uva, que nem sempre aparece dependendo do país.
+Vinho europeu costuma priorizar a região no rótulo (Bordeaux, Chianti, Rioja). Vinho do Novo Mundo costuma destacar a uva (Malbec, Cabernet Sauvignon).
+Saber ler isso já te dá metade do caminho pra escolher melhor.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 14/out</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Documentação da importação</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Antes de qualquer vinho chegar na prateleira, ele passa por uma pilha de documentação: nota fiscal de importação, laudo de análise, registro sanitário, entre outros.
+Processo chato, mas é o que garante que o vinho que chega até você é exatamente o que o produtor engarrafou lá na origem.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 16/out</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Vale ou não vale?</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Guardar vinho na porta da geladeira</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Vale ou não vale: guardar vinho na porta da geladeira?
+Não vale. A porta sofre variação de temperatura toda vez que ela abre, e vinho não gosta de oscilação. O ideal é um lugar fresco, escuro e com temperatura estável.
+Pequeno ajuste, grande diferença no copo.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 12/out</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana: [2-3 vinhos]. Responde aqui se quiser garantir o seu.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 14/out</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor], em [região], [completar com detalhe de história/filosofia].
+Um clássico do catálogo que sempre vale revisitar.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 16/out</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Dica rápida</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Erro ao guardar vinho</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Dica rápida: vinho com rolha natural não gosta de ficar em pé por muito tempo. Deixar deitado mantém a rolha úmida e evita que o ar entre na garrafa.
+Detalhe pequeno que evita estragar uma boa garrafa.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Não precisa de imagem — mensagem só de texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 15/out</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Guia pra não errar na próxima garrafa</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: O guia rápido pra não errar na próxima garrafa
+Oi, [nome]
+Três erros comuns que a gente vê sempre: guardar vinho em pé por muito tempo (rolha seca), guardar na porta da geladeira (oscilação de temperatura) e servir tinto quente demais.
+Pequenos ajustes que fazem diferença real no copo. Se quiser o guia completo, é só responder o quiz e o Mapa do Vinho chega no seu email.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 19/out</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Educação</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Harmonização básica</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Harmonização não precisa ser complicada. Regra básica pra começar: tinto encorpado com carne vermelha, branco com peixe e frutos do mar, espumante praticamente com tudo (inclusive petisco de boteco).
+A lógica por trás: o vinho precisa "aguentar" o peso do prato sem ser dominado nem dominar demais.
+Depois que você pega essa base, dá pra ousar.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Arte gráfica educativa (texto sobre fundo de marca) — gerar com /carrossel ou /post-produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 21/out</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Bastidores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Rotina de importação</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Rotina de quem importa vinho: acompanhar câmbio, calcular imposto antes de fechar pedido, revisar prazo de navio, e torcer pra não ter atraso alfandegário bagunçando o estoque.
+Nada glamouroso, mas é isso que garante que o vinho continua chegando com preço justo.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 23/out</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>O que estamos provando</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Harmonização inusitada</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>O que estamos provando essa semana: [vinho] com [combinação inusitada, ex: pipoca amanteigada, chocolate amargo, queijo azul].
+Combinação que parece estranha no papel mas funciona bem mais do que imagina. Bora testar?</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 19/out</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção pra harmonizar</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana pensada pra harmonizar: [2-3 vinhos com sugestão de prato]. Perfeito pro fim de semana.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 21/out</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História de produtor</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor], em [região], [completar com detalhe de história/filosofia].</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 23/out</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Sugestão de fim de semana</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Churrasco ou happy hour</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana de churrasco ou happy hour? [nome do vinho] é a pedida, combina bem com carne na brasa e queijo.
+Responde aqui que a gente separa.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 22/out</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Guia de harmonização</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: O guia de harmonização que a gente usa aqui
+Oi, [nome]
+Harmonização não precisa de fórmula complicada. O básico: peso do prato combinando com peso do vinho, acidez do vinho cortando gordura do prato, e doce do vinho nunca menos doce que a sobremesa.
+Com essas três regras você já acerta a maioria das combinações. O resto é experimentar.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Formato/Série</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Imagem sugerida</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seg 26/out</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Histórias dos produtores</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor 1], em [região], começou [completar com contexto de origem — família, ano de fundação]. Hoje é reconhecido por [o que faz de diferente].
+Um dos parceiros que carrega mais história dentro do catálogo da comnéctar.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Qua 28/out</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Histórias dos produtores</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em destaque 2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor 2] tem uma trajetória diferente: [completar com detalhe de história/filosofia].
+Duas formas diferentes de fazer vinho com o mesmo compromisso: qualidade antes de volume.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Sex 30/out</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Diário da comnéctar</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Como a comnéctar escolhe parceiros</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Antes de fechar parceria com qualquer produtor, a gente pergunta: essa pessoa faz vinho porque ama o que faz ou só porque é negócio?
+Não dá pra saber com certeza, mas dá pra sentir na consistência das safras e na forma como conta a própria história. É esse filtro que guia quem entra no catálogo.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Foto de bastidores/lifestyle — você, adega, mesa de seleção ou caixas chegando</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Seg 26/out</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Produtores destacados</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Seleção da semana com os produtores que destacamos essa semana: [2-3 vinhos dos produtores em foco].</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Qua 28/out</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>História aprofundada</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Produtor em detalhe</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[nome do produtor], detalhe mais aprofundado da história, processo ou família por trás do vinho.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Foto do produtor/vinícola (pegar no PDF do fornecedor ou site/Instagram do produtor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sex 30/out</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Sugestão de fim de semana</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Vinho do produtor destacado</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Fim de semana com uma dessas histórias na taça: [nome do vinho], do [produtor].
+Bom fim de semana!</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Foto de produto (garrafa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Qui 29/out</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Conheça quem faz o vinho</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Assunto: Conheça quem faz o vinho que você bebe
+Oi, [nome]
+Todo vinho tem um nome de produtor no rótulo, mas poucas vezes a gente para pra conhecer quem está por trás dele. Essa semana separamos duas histórias que valem a leitura: [nome do produtor 1] e [nome do produtor 2].
+Trajetórias diferentes, mesmo compromisso: qualidade antes de volume.
+Um abraço,
+Equipe comnéctar</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Banner de topo com identidade visual da marca (logo + cor vinho de fundo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>